--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05T00:26:02+00:00</t>
+          <t>2026-06-05T11:08:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>49900000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>49900000</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +89,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4353312.698222283</v>
+        <v>5210896.698222283</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>4394948.914498268</v>
+        <v>5252532.914498268</v>
       </c>
     </row>
     <row r="8">
@@ -600,7 +602,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4353312.698222283</v>
+        <v>5210896.698222283</v>
       </c>
     </row>
     <row r="20">
@@ -616,7 +618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>1413020.88273054</v>
+        <v>2270604.88273054</v>
       </c>
     </row>
     <row r="23">
@@ -651,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05T11:08:07+00:00</t>
+          <t>2026-06-08T08:17:48+00:00</t>
         </is>
       </c>
     </row>
@@ -678,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2049,12 +2051,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2064,7 +2066,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -2114,12 +2116,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2129,7 +2131,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2179,12 +2181,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2244,12 +2246,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2309,12 +2311,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2352,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0</v>
@@ -2369,21 +2371,17 @@
       <c r="R25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2393,7 +2391,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -2421,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2438,17 +2436,21 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2508,12 +2510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2523,7 +2525,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2573,17 +2575,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2638,59 +2640,189 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USDC raw on Base (ALM idle)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>857584</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>857584</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>857584</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -3136,6 +3268,1622 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2902299105.715095</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1915988754.642077</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>986310351.0730177</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.03640156294576948</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>96621.74269245965</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>305452.3499058383</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2942299611.449604</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1966157578.098083</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>976142033.3515211</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.03640156294576948</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>95625.62562095902</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>309815.3263347571</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2942299611.449604</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1966600031.289287</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>975699580.1603171</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0.03640156294576948</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>95582.28165894191</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>309815.3263347571</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2942299611.449604</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1991600031.289286</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>950699580.160318</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.03640156294576948</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>93133.21117652884</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>309815.3263347571</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2942299611.449604</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1991600031.289286</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>950699580.160318</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.03640156294576948</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>93133.21117652884</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>309815.3263347571</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2993299611.449604</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2041890772.529286</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>951408838.920318</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>96282.11308634774</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>318614.7466755229</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3092300856.639604</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2092063056.361175</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1000237800.278429</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>101225.4526192667</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>329413.1126278049</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3144300856.639604</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2167281456.252301</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>977019400.3873028</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>98873.88948624684</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>335084.9102748045</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3171300856.639604</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2192507087.798722</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>978793768.8408822</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>99053.45471321935</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>338029.8821299773</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3243944281.747824</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2267736099.057306</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>976208182.6905184</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>98791.79464875504</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>345953.3207376463</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3243944281.747824</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2267736099.057306</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>976208182.6905184</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>98791.79464875504</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>345953.3207376463</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3243944281.747824</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2267736099.057306</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>976208182.6905184</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.03762656294576947</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>98791.79464875504</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>345953.3207376463</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3343944281.747824</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2343349995.666073</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1000594286.081751</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>101033.269462143</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>356629.5577605127</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3343944281.747824</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2393539842.477116</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>950404439.270708</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>95960.86203947759</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>356629.5577605127</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3457644281.747824</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2393747989.762518</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1063896291.985306</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>107937.8111570302</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>369031.1614617405</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3455786805.38163</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2488937052.878606</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>966849752.5030243</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>97621.31980784962</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>368828.5608832187</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3443791778.650098</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2489220053.871007</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>954571724.7790911</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>96381.62639328883</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>367520.226952611</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3437781539.848698</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2489220053.871007</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>948561485.9776911</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>95774.78190412796</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>366864.6719854632</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3452781539.848698</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2489220053.871007</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>963561485.9776911</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>97289.30863729083</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>368500.7674605592</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3458781539.848698</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2489932776.758896</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>968848763.0898014</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>97823.15680608626</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>369155.2056505976</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3458781761.050591</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2490179802.048874</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>968601959.0017172</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.03750000355548933</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.04061250356615579</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.03753906294576947</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>97798.23738013576</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>369155.2297777587</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3463781761.050591</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2490416461.157495</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>973365299.8930957</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.03741368780282747</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>97956.88475052935</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>362859.5216645316</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3462781840.901659</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2440649792.312514</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1022132048.589145</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.03741368780282747</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>102992.8608405092</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>362753.099392382</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3363717598.103676</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2390877078.493134</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>972840519.6105422</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.03741368780282747</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>97904.07226413488</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>352209.6156766036</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3364717598.103676</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2390877078.493134</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>973840519.6105422</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.03741368780282747</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>98004.70959398555</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>352316.046447364</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3365717598.103676</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2390877078.493134</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>974840519.6105422</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.03741368780282747</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>98105.34692383622</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>352422.4772181243</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3322994730.200507</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2341529711.253412</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>981465018.947095</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.03715118780282747</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>98091.47235712872</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>347182.0508362442</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3272990187.731967</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2291743456.043683</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>981246731.6882842</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.03715118780282747</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>98069.655870346</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>341860.0288397996</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3221802586.183359</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2241953580.614037</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>979849005.5693218</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.03715118780282747</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>97929.96162723572</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>336412.0929536084</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3184799649.231286</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>2207150378.300061</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>977649270.9312253</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.03715118780282747</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>97710.11149984418</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>332473.8418534031</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="n">
+        <v>2940291.815491744</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>10336519.98374095</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08T08:17:48+00:00</t>
+          <t>2026-06-09T00:22:37+00:00</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>41636.21627598369</v>
+        <v>45332.82848777324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5252532.914498268</v>
+        <v>5256229.526710057</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T00:22:37+00:00</t>
+          <t>2026-06-09T14:45:47+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T14:45:47+00:00</t>
+          <t>2026-06-09T15:25:18+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T15:25:18+00:00</t>
+          <t>2026-06-09T15:32:40+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T15:32:40+00:00</t>
+          <t>2026-06-09T15:53:20+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T15:53:20+00:00</t>
+          <t>2026-06-09T16:55:12+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>41636.21627598369</v>
+        <v>45332.82848777324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5252532.914498268</v>
+        <v>5256229.526710057</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T00:22:37+00:00</t>
+          <t>2026-06-09T16:55:12+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:12+00:00</t>
+          <t>2026-06-09T19:08:21+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:08:21+00:00</t>
+          <t>2026-06-09T19:50:58+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:50:58+00:00</t>
+          <t>2026-06-09T20:50:34+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T20:50:34+00:00</t>
+          <t>2026-06-09T21:54:09+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:12+00:00</t>
+          <t>2026-06-09T22:25:24+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:24+00:00</t>
+          <t>2026-06-09T23:12:31+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:31+00:00</t>
+          <t>2026-06-09T23:31:24+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:31:24+00:00</t>
+          <t>2026-06-10T01:08:59+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:08:59+00:00</t>
+          <t>2026-06-10T01:49:02+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:49:02+00:00</t>
+          <t>2026-06-10T05:56:15+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T05:56:15+00:00</t>
+          <t>2026-06-10T07:53:56+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T07:53:56+00:00</t>
+          <t>2026-06-10T10:52:07+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:31+00:00</t>
+          <t>2026-06-10T10:52:07+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5210896.698222283</v>
+        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5256229.526710057</v>
+        <v>6668141.822437041</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5210896.698222283</v>
+        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="20">
@@ -618,7 +618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2270604.88273054</v>
+        <v>3682517.178457524</v>
       </c>
     </row>
     <row r="23">
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:07+00:00</t>
+          <t>2026-06-10T14:04:53+00:00</t>
         </is>
       </c>
     </row>
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>798983.3608645581</v>
+        <v>798332.6224423209</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>798983.3608645581</v>
+        <v>798332.6224423209</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>383782.3196085766</v>
+        <v>384433.0580308138</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1047,19 +1047,19 @@
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>164994117.6754281</v>
+        <v>166094117.6754281</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>513190.3775715641</v>
+        <v>516191.0101208151</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>513190.3775715641</v>
+        <v>516191.0101208151</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>625594.5730965375</v>
+        <v>622593.9405472864</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>398874.9083768068</v>
+        <v>398550.0415006478</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>398874.9083768068</v>
+        <v>398550.0415006478</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>191594.9005557068</v>
+        <v>191919.7674318658</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>313936.2460300053</v>
+        <v>313680.5581303178</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>313936.2460300053</v>
+        <v>313680.5581303178</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>260344.8539699948</v>
+        <v>260600.5418696821</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1230,31 +1230,31 @@
         <v>-138267796.0572637</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-1348288.147999676</v>
+        <v>63624.14772730789</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>1411897.309885636</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>63609.1618859599</v>
+        <v>1475521.457612944</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>77820296.86848758</v>
+        <v>77490850.66615129</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>242048.7960136409</v>
+        <v>240827.7971568373</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>242048.7960136409</v>
+        <v>240827.7971568373</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-178439.6341276809</v>
+        <v>1234693.660456107</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>157616.5478947693</v>
+        <v>157488.1758300688</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>157616.5478947693</v>
+        <v>157488.1758300688</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>33437.81041663571</v>
+        <v>33566.1824813362</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>155517.7799068868</v>
+        <v>155391.1172006485</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>155517.7799068868</v>
+        <v>155391.1172006485</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>247225.1800931131</v>
+        <v>247351.8427993514</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>127141.9325754838</v>
+        <v>127038.3808062519</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>127141.9325754838</v>
+        <v>127038.3808062519</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>9752.371987611881</v>
+        <v>9855.923756843762</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>77806.42400195355</v>
+        <v>77743.05393434642</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>77806.42400195355</v>
+        <v>77743.05393434642</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67140.86883795355</v>
+        <v>-67077.49877034643</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>77761.81041589502</v>
+        <v>77698.47668418176</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>77761.81041589502</v>
+        <v>77698.47668418176</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-77536.6530996597</v>
+        <v>-77473.31936794645</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>62681.03919654229</v>
+        <v>62629.98812020096</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>62681.03919654229</v>
+        <v>62629.98812020096</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-12826.36091734772</v>
+        <v>-12775.30984100639</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9701.788589956248</v>
+        <v>9693.886890234897</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9701.788589956248</v>
+        <v>9693.886890234897</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1181.339322911833</v>
+        <v>-1173.437623190483</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3133.389072598707</v>
+        <v>3130.837058675474</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3133.389072598707</v>
+        <v>3130.837058675474</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>311.1442890097251</v>
+        <v>313.6963029329585</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.096876358804</v>
+        <v>1864.577018754073</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.096876358804</v>
+        <v>1864.577018754073</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.096876368241</v>
+        <v>-1864.57701876351</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.31810472118654</v>
+        <v>31.29259743899273</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.31810472118654</v>
+        <v>31.29259743899273</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.31810472118654</v>
+        <v>-31.29259743899273</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3.110355598137735e-09</v>
+        <v>3.10782234401297e-09</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.110355598137735e-09</v>
+        <v>3.10782234401297e-09</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-3.110355598137735e-09</v>
+        <v>-3.10782234401297e-09</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T14:04:53+00:00</t>
+          <t>2026-06-10T15:01:23+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5210896.698222283</v>
+        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5256229.526710057</v>
+        <v>6668141.822437041</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5210896.698222283</v>
+        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="20">
@@ -618,7 +618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2270604.88273054</v>
+        <v>3682517.178457524</v>
       </c>
     </row>
     <row r="23">
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:07+00:00</t>
+          <t>2026-06-10T15:01:23+00:00</t>
         </is>
       </c>
     </row>
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>798983.3608645581</v>
+        <v>798332.6224423209</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>798983.3608645581</v>
+        <v>798332.6224423209</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>383782.3196085766</v>
+        <v>384433.0580308138</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1047,19 +1047,19 @@
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>164994117.6754281</v>
+        <v>166094117.6754281</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>513190.3775715641</v>
+        <v>516191.0101208151</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>513190.3775715641</v>
+        <v>516191.0101208151</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>625594.5730965375</v>
+        <v>622593.9405472864</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>398874.9083768068</v>
+        <v>398550.0415006478</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>398874.9083768068</v>
+        <v>398550.0415006478</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>191594.9005557068</v>
+        <v>191919.7674318658</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>313936.2460300053</v>
+        <v>313680.5581303178</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>313936.2460300053</v>
+        <v>313680.5581303178</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>260344.8539699948</v>
+        <v>260600.5418696821</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1230,31 +1230,31 @@
         <v>-138267796.0572637</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-1348288.147999676</v>
+        <v>63624.14772730789</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>1411897.309885636</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>63609.1618859599</v>
+        <v>1475521.457612944</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>77820296.86848758</v>
+        <v>77490850.66615129</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>242048.7960136409</v>
+        <v>240827.7971568373</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>242048.7960136409</v>
+        <v>240827.7971568373</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-178439.6341276809</v>
+        <v>1234693.660456107</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>157616.5478947693</v>
+        <v>157488.1758300688</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>157616.5478947693</v>
+        <v>157488.1758300688</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>33437.81041663571</v>
+        <v>33566.1824813362</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>155517.7799068868</v>
+        <v>155391.1172006485</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>155517.7799068868</v>
+        <v>155391.1172006485</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>247225.1800931131</v>
+        <v>247351.8427993514</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>127141.9325754838</v>
+        <v>127038.3808062519</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>127141.9325754838</v>
+        <v>127038.3808062519</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>9752.371987611881</v>
+        <v>9855.923756843762</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>77806.42400195355</v>
+        <v>77743.05393434642</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>77806.42400195355</v>
+        <v>77743.05393434642</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67140.86883795355</v>
+        <v>-67077.49877034643</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>77761.81041589502</v>
+        <v>77698.47668418176</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>77761.81041589502</v>
+        <v>77698.47668418176</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-77536.6530996597</v>
+        <v>-77473.31936794645</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>62681.03919654229</v>
+        <v>62629.98812020096</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>62681.03919654229</v>
+        <v>62629.98812020096</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-12826.36091734772</v>
+        <v>-12775.30984100639</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9701.788589956248</v>
+        <v>9693.886890234897</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9701.788589956248</v>
+        <v>9693.886890234897</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1181.339322911833</v>
+        <v>-1173.437623190483</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3133.389072598707</v>
+        <v>3130.837058675474</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3133.389072598707</v>
+        <v>3130.837058675474</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>311.1442890097251</v>
+        <v>313.6963029329585</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.096876358804</v>
+        <v>1864.577018754073</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.096876358804</v>
+        <v>1864.577018754073</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.096876368241</v>
+        <v>-1864.57701876351</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.31810472118654</v>
+        <v>31.29259743899273</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.31810472118654</v>
+        <v>31.29259743899273</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.31810472118654</v>
+        <v>-31.29259743899273</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3.110355598137735e-09</v>
+        <v>3.10782234401297e-09</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.110355598137735e-09</v>
+        <v>3.10782234401297e-09</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-3.110355598137735e-09</v>
+        <v>-3.10782234401297e-09</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -84,12 +85,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -653,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T15:01:23+00:00</t>
+          <t>2026-06-23T20:31:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2854,185 +2857,378 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2940291.815491744</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>6395006.500245043</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>976625153.4840184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9335298.315736787</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>973729805.9195307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2895347.564487692</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.04030997361747411</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (tbill_3m), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.03686666666666667</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>10336519.98374095</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0.0372972837362202</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>2940291.815491744</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.03730709608600075</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-7396228.168249207</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-30.02877531473362</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>232061.9088781188</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3172353.724369863</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>232061.9088781188</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ramp_months</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>24</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Rate (APY)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ref_rate_kind</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tbill_3m</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>973729805.9195307</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.0372972837362202</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2930876.164041317</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2895347.564487692</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.04030997361747411</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>9415.651451270996</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6395006.500245043</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>9335298.315736787</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>10336519.98374095</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-7396228.168249207</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ramp_months</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ref_rate_kind</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tbill_3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>3 (SoM) → 3 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -3296,7 +3492,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4849,7 +5045,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T20:31:05+00:00</t>
+          <t>2026-06-23T21:34:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>232061.9088781188</v>
+        <v>232061.9088782076</v>
       </c>
     </row>
     <row r="15">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3172353.724369863</v>
+        <v>3172353.724369952</v>
       </c>
     </row>
     <row r="16">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>232061.9088781188</v>
+        <v>232061.9088782076</v>
       </c>
     </row>
     <row r="19">
@@ -3008,11 +3008,6 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rate (APY)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
           <t>CoF (USD)</t>
         </is>
       </c>
@@ -3026,11 +3021,8 @@
       <c r="B20" s="5" t="n">
         <v>973729805.9195307</v>
       </c>
-      <c r="C20" s="6" t="n">
-        <v>0.0372972837362202</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2930876.164041317</v>
+      <c r="C20" s="3" t="n">
+        <v>2930876.164040472</v>
       </c>
     </row>
     <row r="21">
@@ -3042,11 +3034,8 @@
       <c r="B21" s="5" t="n">
         <v>2895347.564487692</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <v>0.04030997361747411</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>9415.651451270996</v>
+      <c r="C21" s="3" t="n">
+        <v>9415.651451271397</v>
       </c>
     </row>
     <row r="23">

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -84,12 +85,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -653,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T15:01:23+00:00</t>
+          <t>2026-06-23T21:34:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2854,185 +2857,367 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2940291.815491744</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>6395006.500245043</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>976625153.4840184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9335298.315736787</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>973729805.9195307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2895347.564487692</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.04030997361747411</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (tbill_3m), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.03686666666666667</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>10336519.98374095</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0.0372972837362202</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>2940291.815491744</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.03730709608600075</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-7396228.168249207</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-30.02877531473362</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>232061.9088782076</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3172353.724369952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>232061.9088782076</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ramp_months</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>24</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ref_rate_kind</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tbill_3m</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>973729805.9195307</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2930876.164040472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2895347.564487692</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>9415.651451271397</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6395006.500245043</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>9335298.315736787</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>10336519.98374095</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-7396228.168249207</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ramp_months</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ref_rate_kind</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tbill_3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>3 (SoM) → 3 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -3296,7 +3481,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4849,7 +5034,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T21:34:40+00:00</t>
+          <t>2026-06-23T22:22:00+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,168 +505,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>6668141.822437041</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>125090.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>6793231.992437041</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>6395006.500245043</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>9335298.315736787</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-7396228.168249207</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>10336519.98374095</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>6622808.993949268</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-2940291.815491744</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>3682517.178457524</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2026-04-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
+          <t>2026-04-01 → 2026-04-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T22:22:00+00:00</t>
+          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:22:00+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,168 +505,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>6668141.822437041</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>125090.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>6793231.992437041</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>6395006.500245043</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>9335298.315736787</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>2940291.815491744</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2940291.815491744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-7396228.168249207</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>10336519.98374095</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>6622808.993949268</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>6622808.993949268</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-2940291.815491744</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>3682517.178457524</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2026-04-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
+          <t>2026-04-01 → 2026-04-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T21:34:40+00:00</t>
+          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:22:00+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-23T22:22:00+00:00</t>
+          <t>2026-07-03T06:32:36+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-03T06:32:36+00:00</t>
+          <t>2026-07-07T14:51:41+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:41+00:00</t>
+          <t>2026-07-08T18:39:43+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-08T18:39:43+00:00</t>
+          <t>2026-07-09T08:05:26+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6622808.993949268</v>
+        <v>6622808.993949277</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>6793231.992437041</v>
+        <v>6793231.992437051</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6622808.993949268</v>
+        <v>6622808.993949277</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>3682517.178457524</v>
+        <v>3682517.178457533</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-09T08:05:26+00:00</t>
+          <t>2026-07-10T11:17:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>798332.6224423209</v>
+        <v>782704.0391053858</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>798332.6224423209</v>
+        <v>782704.0391053858</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>384433.0580308138</v>
+        <v>400061.641367749</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>516191.0101208151</v>
+        <v>506085.7808057839</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>516191.0101208151</v>
+        <v>506085.7808057839</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>622593.9405472864</v>
+        <v>632699.1698623176</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>398550.0415006478</v>
+        <v>390747.8142554723</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>398550.0415006478</v>
+        <v>390747.8142554723</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>191919.7674318658</v>
+        <v>199721.9946770412</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>313680.5581303178</v>
+        <v>307539.7809578678</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>313680.5581303178</v>
+        <v>307539.7809578678</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>260600.5418696821</v>
+        <v>266741.3190421322</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>240827.7971568373</v>
+        <v>236113.2243185113</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>240827.7971568373</v>
+        <v>236113.2243185113</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1234693.660456107</v>
+        <v>1239408.233294433</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>157488.1758300688</v>
+        <v>154405.1036727363</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>157488.1758300688</v>
+        <v>154405.1036727363</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>33566.1824813362</v>
+        <v>36649.25463866865</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>155391.1172006485</v>
+        <v>152349.0981765979</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>155391.1172006485</v>
+        <v>152349.0981765979</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>247351.8427993514</v>
+        <v>250393.861823402</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>127038.3808062519</v>
+        <v>124551.4100053521</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>127038.3808062519</v>
+        <v>124551.4100053521</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>9855.923756843762</v>
+        <v>12342.89455774355</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>77743.05393434642</v>
+        <v>76221.11462844194</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>77743.05393434642</v>
+        <v>76221.11462844194</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67077.49877034643</v>
+        <v>-65555.55946444193</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>77698.47668418176</v>
+        <v>76177.41004619731</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>77698.47668418176</v>
+        <v>76177.41004619731</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-77473.31936794645</v>
+        <v>-75952.25272996201</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>62629.98812020096</v>
+        <v>61403.91021581402</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>62629.98812020096</v>
+        <v>61403.91021581402</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-12775.30984100639</v>
+        <v>-11549.23193661945</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1674,12 +1674,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1689,44 +1689,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3954260.398216645</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5004060.193602587</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1049799.795385942</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>8520.449267044414</v>
+        <v>3.096e-20</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>8520.449267044414</v>
+        <v>3.096e-20</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>3119189.521534131</v>
+        <v>18891058.29432581</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9693.886890234897</v>
+        <v>57560.71389484152</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9693.886890234897</v>
+        <v>57560.71389484152</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1173.437623190483</v>
+        <v>-57560.71389484152</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1739,17 +1739,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1758,40 +1758,40 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1007405.415147632</v>
+        <v>3954260.398216645</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1010849.948509241</v>
+        <v>5004060.193602587</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>1049799.795385942</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>8520.449267044414</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>8520.449267044414</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1007405.415147632</v>
+        <v>3119189.521534131</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3130.837058675474</v>
+        <v>9504.114212952372</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3130.837058675474</v>
+        <v>9504.114212952372</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>313.6963029329585</v>
+        <v>-983.6649459079571</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1804,59 +1804,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>9999494.265490999</v>
+        <v>1007405.415147632</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>1010849.948509241</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-9999494.265490999</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-9.437415e-09</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-9.437415e-09</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>599962.5500943019</v>
+        <v>1007405.415147632</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1864.577018754073</v>
+        <v>3069.546129919258</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1864.577018754073</v>
+        <v>3069.546129919258</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1864.57701876351</v>
+        <v>374.9872316891734</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1869,12 +1869,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>9999494.265490999</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>-9999494.265490999</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1909,19 +1909,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>599962.5500943046</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.29259743899273</v>
+        <v>1828.075068931985</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.29259743899273</v>
+        <v>1828.075068931985</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.29259743899273</v>
+        <v>-1828.075068931985</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1934,12 +1934,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1949,14 +1949,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1974,19 +1974,19 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3.10782234401297e-09</v>
+        <v>30.67999693494682</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.10782234401297e-09</v>
+        <v>30.67999693494682</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-3.10782234401297e-09</v>
+        <v>-30.67999693494682</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1999,12 +1999,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,14 +2014,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -2039,19 +2039,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>3.046981963531957e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0</v>
+        <v>3.046981963531957e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>-3.046981963531957e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2064,12 +2064,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2194,12 +2194,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6622808.993949268</v>
+        <v>6622808.993949277</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>6793231.992437041</v>
+        <v>6793231.992437051</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6622808.993949268</v>
+        <v>6622808.993949277</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>3682517.178457524</v>
+        <v>3682517.178457533</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:41+00:00</t>
+          <t>2026-07-10T11:17:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>798332.6224423209</v>
+        <v>782704.0391053858</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>798332.6224423209</v>
+        <v>782704.0391053858</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>384433.0580308138</v>
+        <v>400061.641367749</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>516191.0101208151</v>
+        <v>506085.7808057839</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>516191.0101208151</v>
+        <v>506085.7808057839</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>622593.9405472864</v>
+        <v>632699.1698623176</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>398550.0415006478</v>
+        <v>390747.8142554723</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>398550.0415006478</v>
+        <v>390747.8142554723</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>191919.7674318658</v>
+        <v>199721.9946770412</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>313680.5581303178</v>
+        <v>307539.7809578678</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>313680.5581303178</v>
+        <v>307539.7809578678</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>260600.5418696821</v>
+        <v>266741.3190421322</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>240827.7971568373</v>
+        <v>236113.2243185113</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>240827.7971568373</v>
+        <v>236113.2243185113</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1234693.660456107</v>
+        <v>1239408.233294433</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>157488.1758300688</v>
+        <v>154405.1036727363</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>157488.1758300688</v>
+        <v>154405.1036727363</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>33566.1824813362</v>
+        <v>36649.25463866865</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>155391.1172006485</v>
+        <v>152349.0981765979</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>155391.1172006485</v>
+        <v>152349.0981765979</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>247351.8427993514</v>
+        <v>250393.861823402</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>127038.3808062519</v>
+        <v>124551.4100053521</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>127038.3808062519</v>
+        <v>124551.4100053521</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>9855.923756843762</v>
+        <v>12342.89455774355</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>77743.05393434642</v>
+        <v>76221.11462844194</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>77743.05393434642</v>
+        <v>76221.11462844194</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67077.49877034643</v>
+        <v>-65555.55946444193</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>77698.47668418176</v>
+        <v>76177.41004619731</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>77698.47668418176</v>
+        <v>76177.41004619731</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-77473.31936794645</v>
+        <v>-75952.25272996201</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>62629.98812020096</v>
+        <v>61403.91021581402</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>62629.98812020096</v>
+        <v>61403.91021581402</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-12775.30984100639</v>
+        <v>-11549.23193661945</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1674,12 +1674,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1689,44 +1689,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3954260.398216645</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5004060.193602587</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1049799.795385942</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>8520.449267044414</v>
+        <v>3.096e-20</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>8520.449267044414</v>
+        <v>3.096e-20</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>3119189.521534131</v>
+        <v>18891058.29432581</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9693.886890234897</v>
+        <v>57560.71389484152</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9693.886890234897</v>
+        <v>57560.71389484152</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1173.437623190483</v>
+        <v>-57560.71389484152</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1739,17 +1739,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1758,40 +1758,40 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1007405.415147632</v>
+        <v>3954260.398216645</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1010849.948509241</v>
+        <v>5004060.193602587</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>1049799.795385942</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>8520.449267044414</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3444.533361608432</v>
+        <v>8520.449267044414</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1007405.415147632</v>
+        <v>3119189.521534131</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3130.837058675474</v>
+        <v>9504.114212952372</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3130.837058675474</v>
+        <v>9504.114212952372</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>313.6963029329585</v>
+        <v>-983.6649459079571</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1804,59 +1804,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>9999494.265490999</v>
+        <v>1007405.415147632</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>1010849.948509241</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-9999494.265490999</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-9.437415e-09</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-9.437415e-09</v>
+        <v>3444.533361608432</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>599962.5500943019</v>
+        <v>1007405.415147632</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1864.577018754073</v>
+        <v>3069.546129919258</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1864.577018754073</v>
+        <v>3069.546129919258</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1864.57701876351</v>
+        <v>374.9872316891734</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1869,12 +1869,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>9999494.265490999</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>-9999494.265490999</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1909,19 +1909,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>599962.5500943046</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.29259743899273</v>
+        <v>1828.075068931985</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.29259743899273</v>
+        <v>1828.075068931985</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.29259743899273</v>
+        <v>-1828.075068931985</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1934,12 +1934,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1949,14 +1949,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1974,19 +1974,19 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1e-06</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3.10782234401297e-09</v>
+        <v>30.67999693494682</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.10782234401297e-09</v>
+        <v>30.67999693494682</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-3.10782234401297e-09</v>
+        <v>-30.67999693494682</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1999,12 +1999,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,14 +2014,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -2039,19 +2039,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>3.046981963531957e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0</v>
+        <v>3.046981963531957e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>-3.046981963531957e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2064,12 +2064,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2194,12 +2194,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9335298.315736787</v>
+        <v>9341951.061718298</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="16">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-7396228.168249207</v>
+        <v>-7396515.160294596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>10336519.98374095</v>
+        <v>10343459.72176785</v>
       </c>
     </row>
     <row r="19">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-2940291.815491744</v>
+        <v>-2946944.561473255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>3682517.178457533</v>
+        <v>3675864.432476022</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:36+00:00</t>
+          <t>2026-07-31T00:11:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782704.0391053858</v>
+        <v>784474.9963700477</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782704.0391053858</v>
+        <v>784474.9963700477</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>400061.641367749</v>
+        <v>398290.6841030871</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>506085.7808057839</v>
+        <v>507230.8576742826</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>506085.7808057839</v>
+        <v>507230.8576742826</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>632699.1698623176</v>
+        <v>631554.092993819</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>390747.8142554723</v>
+        <v>391631.9258043247</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>390747.8142554723</v>
+        <v>391631.9258043247</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>199721.9946770412</v>
+        <v>198837.8831281889</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>307539.7809578678</v>
+        <v>308235.6248299428</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>307539.7809578678</v>
+        <v>308235.6248299428</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>266741.3190421322</v>
+        <v>266045.4751700572</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>236113.2243185113</v>
+        <v>236647.4574500632</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>236113.2243185113</v>
+        <v>236647.4574500632</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1239408.233294433</v>
+        <v>1238874.000162881</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>154405.1036727363</v>
+        <v>154754.4628511592</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>154405.1036727363</v>
+        <v>154754.4628511592</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>36649.25463866865</v>
+        <v>36299.89546024581</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>152349.0981765979</v>
+        <v>152693.8054078125</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>152349.0981765979</v>
+        <v>152693.8054078125</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>250393.861823402</v>
+        <v>250049.1545921874</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>124551.4100053521</v>
+        <v>124833.2217928893</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>124551.4100053521</v>
+        <v>124833.2217928893</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>12342.89455774355</v>
+        <v>12061.08277020638</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>76221.11462844194</v>
+        <v>76393.5736039011</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>76221.11462844194</v>
+        <v>76393.5736039011</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-65555.55946444193</v>
+        <v>-65728.01843990111</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>76177.41004619731</v>
+        <v>76349.77013504857</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>76177.41004619731</v>
+        <v>76349.77013504857</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-75952.25272996201</v>
+        <v>-76124.61281881326</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>61403.91021581402</v>
+        <v>61542.84357432796</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>61403.91021581402</v>
+        <v>61542.84357432796</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-11549.23193661945</v>
+        <v>-11688.16529513339</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>57560.71389484152</v>
+        <v>57690.95158282855</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>57560.71389484152</v>
+        <v>57690.95158282855</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-57560.71389484152</v>
+        <v>-57690.95158282855</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>9504.114212952372</v>
+        <v>9525.618356624407</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>9504.114212952372</v>
+        <v>9525.618356624407</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-983.6649459079571</v>
+        <v>-1005.169089579991</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3069.546129919258</v>
+        <v>3076.491328546582</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3069.546129919258</v>
+        <v>3076.491328546582</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>374.9872316891734</v>
+        <v>368.04203306185</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1915,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1828.075068931985</v>
+        <v>1832.211297521494</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1828.075068931985</v>
+        <v>1832.211297521494</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-1828.075068931985</v>
+        <v>-1832.211297521494</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>30.67999693494682</v>
+        <v>30.74941393133009</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>30.67999693494682</v>
+        <v>30.74941393133009</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-30.67999693494682</v>
+        <v>-30.74941393133009</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.046981963531957e-09</v>
+        <v>3.05387610815625e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.046981963531957e-09</v>
+        <v>3.05387610815625e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.046981963531957e-09</v>
+        <v>-3.05387610815625e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.03686666666666667</v>
+        <v>0.03696666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.0372972837362202</v>
+        <v>0.03738478373622021</v>
       </c>
     </row>
     <row r="11">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03730709608600075</v>
+        <v>0.03739298437091029</v>
       </c>
     </row>
     <row r="12">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-30.02877531473362</v>
+        <v>-29.16989246563823</v>
       </c>
     </row>
     <row r="13">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>232061.9088782076</v>
+        <v>225409.1628966965</v>
       </c>
     </row>
     <row r="15">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="17">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>232061.9088782076</v>
+        <v>225409.1628966965</v>
       </c>
     </row>
     <row r="19">
@@ -3032,7 +3032,7 @@
         <v>973729805.9195307</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2930876.164040472</v>
+        <v>2937528.910021984</v>
       </c>
     </row>
     <row r="21">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="25">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9335298.315736787</v>
+        <v>9341951.061718298</v>
       </c>
     </row>
     <row r="28">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10336519.98374095</v>
+        <v>10343459.72176785</v>
       </c>
     </row>
     <row r="31">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="32">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-7396228.168249207</v>
+        <v>-7396515.160294596</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -3610,16 +3610,16 @@
         <v>3</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.037</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>96621.74269245965</v>
+        <v>99358.3041616807</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>305452.3499058383</v>
+        <v>308226.8939083866</v>
       </c>
     </row>
     <row r="7">
@@ -3659,16 +3659,16 @@
         <v>3</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.037</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>95625.62562095902</v>
+        <v>98333.97464522987</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>309815.3263347571</v>
+        <v>312589.8703373055</v>
       </c>
     </row>
     <row r="8">
@@ -3708,16 +3708,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>95582.28165894191</v>
+        <v>98514.87317923989</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>309815.3263347571</v>
+        <v>312820.9559157559</v>
       </c>
     </row>
     <row r="9">
@@ -3757,16 +3757,16 @@
         <v>3</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>93133.21117652884</v>
+        <v>95990.66195730185</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>309815.3263347571</v>
+        <v>312820.9559157559</v>
       </c>
     </row>
     <row r="10">
@@ -3806,16 +3806,16 @@
         <v>3</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>93133.21117652884</v>
+        <v>95990.66195730185</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>309815.3263347571</v>
+        <v>312820.9559157559</v>
       </c>
     </row>
     <row r="11">
@@ -3904,16 +3904,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>101225.4526192667</v>
+        <v>100994.3864748262</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>329413.1126278049</v>
+        <v>329182.0464833644</v>
       </c>
     </row>
     <row r="13">
@@ -3953,16 +3953,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>98873.88948624684</v>
+        <v>98196.56420288843</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>335084.9102748045</v>
+        <v>334391.6535359005</v>
       </c>
     </row>
     <row r="14">
@@ -4002,16 +4002,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0368</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03727656294576948</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>99053.45471321935</v>
+        <v>98148.6761589438</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>338029.8821299773</v>
+        <v>337105.500934389</v>
       </c>
     </row>
     <row r="15">
@@ -4051,16 +4051,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>98791.79464875504</v>
+        <v>98115.03174753163</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>345953.3207376463</v>
+        <v>345260.0639987424</v>
       </c>
     </row>
     <row r="16">
@@ -4100,16 +4100,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>98791.79464875504</v>
+        <v>98115.03174753163</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>345953.3207376463</v>
+        <v>345260.0639987424</v>
       </c>
     </row>
     <row r="17">
@@ -4149,16 +4149,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>98791.79464875504</v>
+        <v>98115.03174753163</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>345953.3207376463</v>
+        <v>345260.0639987424</v>
       </c>
     </row>
     <row r="18">
@@ -4345,16 +4345,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>97621.31980784962</v>
+        <v>97397.89477351782</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>368828.5608832187</v>
+        <v>368597.4753047682</v>
       </c>
     </row>
     <row r="22">
@@ -4394,16 +4394,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>96381.62639328883</v>
+        <v>96161.03863409584</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>367520.226952611</v>
+        <v>367289.1413741605</v>
       </c>
     </row>
     <row r="23">
@@ -4443,16 +4443,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>95774.78190412796</v>
+        <v>95555.583024445</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>366864.6719854632</v>
+        <v>366633.5864070128</v>
       </c>
     </row>
     <row r="24">
@@ -4492,16 +4492,16 @@
         <v>3</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>97289.30863729083</v>
+        <v>97066.64347393114</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>368500.7674605592</v>
+        <v>368269.6818821088</v>
       </c>
     </row>
     <row r="25">
@@ -4590,16 +4590,16 @@
         <v>3</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>97798.23738013576</v>
+        <v>97350.55866490623</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>369155.2297777587</v>
+        <v>368693.0391832952</v>
       </c>
     </row>
     <row r="27">
@@ -4639,16 +4639,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>97956.88475052935</v>
+        <v>97506.95023874096</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>362859.5216645316</v>
+        <v>362397.2753610751</v>
       </c>
     </row>
     <row r="28">
@@ -4688,16 +4688,16 @@
         <v>3</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>102992.8608405092</v>
+        <v>102530.6145370527</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>362753.099392382</v>
+        <v>362290.8530889255</v>
       </c>
     </row>
     <row r="29">
@@ -4737,16 +4737,16 @@
         <v>3</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>97904.07226413488</v>
+        <v>97454.38033009223</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>352209.6156766036</v>
+        <v>351747.3693731471</v>
       </c>
     </row>
     <row r="30">
@@ -4786,16 +4786,16 @@
         <v>3</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>98004.70959398555</v>
+        <v>97554.55541363943</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>352316.046447364</v>
+        <v>351853.8001439075</v>
       </c>
     </row>
     <row r="31">
@@ -4835,16 +4835,16 @@
         <v>3</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>98105.34692383622</v>
+        <v>97654.73049718664</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>352422.4772181243</v>
+        <v>351960.2309146678</v>
       </c>
     </row>
     <row r="32">
@@ -5062,10 +5062,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="10" t="n">
-        <v>2940291.815491744</v>
+        <v>2946944.561473255</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>10336519.98374095</v>
+        <v>10343459.72176785</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -2918,7 +2918,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
+++ b/settlements/grove/2026-04/grove_settlement_april_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6622808.993949277</v>
+        <v>6540434.835030718</v>
       </c>
     </row>
     <row r="5">
@@ -515,168 +515,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>6793231.992437051</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>17001.12794103559</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>6727858.961459527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2946944.561473255</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>6395006.500245043</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>9341951.061718298</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>2946944.561473255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2946944.561473255</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-7396515.160294596</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>10343459.72176785</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>6622808.993949277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>6540434.835030718</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-2946944.561473255</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
-        <v>3675864.432476022</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2026-04-30 (30 days)</t>
-        </is>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
+        <v>3593490.273557463</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
+          <t>2026-04-01 → 2026-04-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-31T00:11:36+00:00</t>
+          <t>avalanche_c=84298393, base=45402126, ethereum=24996367, monad=71616121, plume=65382097</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:21:56+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
@@ -693,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1302,19 +1312,19 @@
         <v>50674767.8590638</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>50865822.2173752</v>
+        <v>50783448.05845664</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>191054.358311405</v>
+        <v>108680.1993928453</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>191054.358311405</v>
+        <v>108680.1993928453</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>191054.358311405</v>
+        <v>108680.1993928453</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
@@ -1332,7 +1342,7 @@
         <v>154754.4628511592</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>36299.89546024581</v>
+        <v>-46074.26345831385</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -2783,59 +2793,189 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -2928,7 +3068,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (tbill_3m), period avg</t>
+          <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
